--- a/file_lain/template_import_bank_soal.xlsx
+++ b/file_lain/template_import_bank_soal.xlsx
@@ -1,42 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FILE TUGAS AKHIR\~APLIKASI\Website CAT\file_lain\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B45592-DC38-4810-9D9B-3184F1DD4EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
     <sheet name="Panduan" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Soal</t>
+  </si>
+  <si>
+    <t>Opsi A</t>
+  </si>
+  <si>
+    <t>Opsi B</t>
+  </si>
+  <si>
+    <t>Opsi C</t>
+  </si>
+  <si>
+    <t>Opsi D</t>
+  </si>
+  <si>
+    <t>Opsi E</t>
+  </si>
+  <si>
+    <t>Jawaban</t>
+  </si>
+  <si>
+    <t>Gambar</t>
+  </si>
+  <si>
+    <t>single_choice</t>
+  </si>
+  <si>
+    <t>Siapa presiden pertama Indonesia?</t>
+  </si>
+  <si>
+    <t>Soekarno</t>
+  </si>
+  <si>
+    <t>Soeharto</t>
+  </si>
+  <si>
+    <t>B.J. Habibie</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>multi_choice</t>
+  </si>
+  <si>
+    <t>Yang termasuk bilangan prima adalah...</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>A,B,D</t>
+  </si>
+  <si>
+    <t>benar_salah</t>
+  </si>
+  <si>
+    <t>Tentukan benar/salah pernyataan berikut.</t>
+  </si>
+  <si>
+    <t>Bumi berbentuk bulat</t>
+  </si>
+  <si>
+    <t>Matahari mengelilingi Bumi</t>
+  </si>
+  <si>
+    <t>Air mendidih pada 100°C</t>
+  </si>
+  <si>
+    <t>B,S,B</t>
+  </si>
+  <si>
+    <t>PANDUAN FORMAT IMPORT BANK SOAL</t>
+  </si>
+  <si>
+    <t>Kolom di sheet "Soal" (baris pertama = header):</t>
+  </si>
+  <si>
+    <t>single_choice | multi_choice | benar_salah</t>
+  </si>
+  <si>
+    <t>Teks pertanyaan (opsional untuk benar_salah)</t>
+  </si>
+  <si>
+    <t>Opsi A s/d F</t>
+  </si>
+  <si>
+    <t>Isi opsi atau pernyataan. Minimal 3 untuk single/multi, minimal 1 untuk benar_salah</t>
+  </si>
+  <si>
+    <t>Single: satu huruf A-F. Multi: dipisah koma contoh A,B,D. Benar/Salah: B atau S per pernyataan, contoh B,B,S</t>
+  </si>
+  <si>
+    <t>URL gambar (opsional)</t>
+  </si>
+  <si>
+    <t>Contoh nilai Kategori: single_choice, multi_choice, benar_salah</t>
+  </si>
+  <si>
+    <t>Untuk benar_salah, isi Jawaban dengan B (Benar) dan S (Salah) sesuai urutan Opsi A, B, C, ...</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,13 +177,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,227 +516,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" customWidth="1"/>
+    <col min="2" max="2" width="40.796875" customWidth="1"/>
+    <col min="3" max="6" width="25.796875" customWidth="1"/>
+    <col min="7" max="7" width="15.796875" customWidth="1"/>
+    <col min="8" max="8" width="12.796875" customWidth="1"/>
+    <col min="9" max="9" width="20.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Kategori</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Soal</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Opsi A</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Opsi B</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Opsi C</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Opsi D</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Opsi E</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Opsi F</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Jawaban</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Gambar</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>single_choice</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Siapa presiden pertama Indonesia?</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Soekarno</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Soeharto</v>
-      </c>
-      <c r="E2" t="str">
-        <v>B.J. Habibie</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>A</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>multi_choice</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Yang termasuk bilangan prima adalah...</v>
-      </c>
-      <c r="C3" t="str">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>A,B,D</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>benar_salah</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Tentukan benar/salah pernyataan berikut.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Bumi berbentuk bulat</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Matahari mengelilingi Bumi</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Air mendidih pada 100°C</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>B,S,B</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:G4 H1:I4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="50.796875" customWidth="1"/>
+    <col min="2" max="2" width="60.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PANDUAN FORMAT IMPORT BANK SOAL</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Kolom di sheet "Soal" (baris pertama = header):</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Kategori</v>
-      </c>
-      <c r="B4" t="str">
-        <v>single_choice | multi_choice | benar_salah</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Soal</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Teks pertanyaan (opsional untuk benar_salah)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Opsi A s/d F</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Isi opsi atau pernyataan. Minimal 3 untuk single/multi, minimal 1 untuk benar_salah</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Jawaban</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Single: satu huruf A-F. Multi: dipisah koma contoh A,B,D. Benar/Salah: B atau S per pernyataan, contoh B,B,S</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Gambar</v>
-      </c>
-      <c r="B8" t="str">
-        <v>URL gambar (opsional)</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Contoh nilai Kategori: single_choice, multi_choice, benar_salah</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Untuk benar_salah, isi Jawaban dengan B (Benar) dan S (Salah) sesuai urutan Opsi A, B, C, ...</v>
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError sqref="A1:B11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>